--- a/TESTS/zlit_7_kiplinh.xlsx
+++ b/TESTS/zlit_7_kiplinh.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Британський письменник і поет народжений в Індії — лауреат Нобелівської премії 1907 р. перший британець</t>
+          <t>Британський письменник і поет народжений в Індії</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Індія — Кіплінг народився і виріс там і цей досвід пронизує більшість його творів</t>
+          <t>Індія</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Суперечливе — його талант незаперечний але деякі твори відображають колоніальні погляди своєї епохи</t>
+          <t>Суперечливе</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>«Захід є Захід а Схід є Схід і разом їм не зійтись» — але балада показує що між людьми це можливо</t>
+          <t>«Захід є Захід а Схід є Схід і разом їм не зійтись»</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -813,6 +843,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Дидактичний вірш у формі настанов батька синові — кодекс людської зрілості і гідності</t>
+          <t>Дидактичний вірш у формі настанов батька синові</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>«Якщо ти зможеш все це — ти будеш Людиною сину мій» — це вінець усього переліку чеснот</t>
+          <t>«Якщо ти зможеш все це</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Де народився і виріс Редьярд Кіплінг?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У Лондоні</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В Індії — він народився в Бомбеї і виріс серед двох культур: британської і індійської</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>В Австралії</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В Африці</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Яку Нобелівську відзнаку отримав Кіплінг?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Премію з фізики</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Нобелівську премію з літератури у 1907 році — перший британець удостоєний нею</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Премію миру</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нобелівської не отримував</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому оцінка спадщини Кіплінга сучасними критиками є суперечливою?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо він погано писав</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо поруч з геніальними текстами є твори, що відображають колоніальний світогляд епохи</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо він мало написав</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо він навмисно образив критиків</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Про яку конкретну зустріч розповідає «Балада про Схід і Захід»?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зустріч двох купців</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Погоню британського офіцера за ватажком афганців Камалем, що вкрав коня</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Битву армій</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Переговори дипломатів</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Як поводив себе Камаль під час переслідування?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Тікав у страху</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зупинився, обернувся і вийшов назустріч офіцеру — виявивши повагу до сміливця</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Став битись з засідки</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Здався без бою</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Який жест зробив Камаль наприкінці зустрічі з британським офіцером?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Попросив викуп</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Відпустив офіцера і відправив свого сина служити до британців як знак поваги</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Оголосив війну</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Запропонував обмінятись зброєю</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Що означає парадоксальна фраза з початку балади: «Захід є Захід, а Схід є Схід, і разом їм не зійтись»?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Схід і Захід ніколи не можуть мати нічого спільного</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Культури різні, але фраза спростовується самим сюжетом: шляхетні люди знаходять спільну мову поза межами цього</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Кіплінг ненавидів Схід</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Фраза означає саме те, що написано</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Коли, за фіналом балади, «немає ні Сходу ні Заходу»?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніколи</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Коли двоє людей дивляться одне одному в вічі — справжня шляхетність не знає кордонів</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише під час миру</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише між солдатами</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Якою поетичною формою написана «Балада про Схід і Захід»?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вільним віршем</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Баладою з парними римами і рефреном, що нагадує народну пісню</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сонетом</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Одою без рими</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Якій особі адресований вірш «Якщо…» — формально?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Дочці</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Синові — хоча звертання до будь-якої молодої людини</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Другові</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Читачеві абстрактно</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Яку конструкцію повторює вірш «Якщо…» в кожному катрені?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Питання і відповідь</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Умовні речення «якщо ти зможеш…», де кожне описує випробування</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Протиставлення без умови</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Порівняння</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що, за Кіплінгом, найважче зберегти у хвилину народного тріумфу чи поразки?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гроші і майно</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Рівновагу духу — не впасти у зарозумілість від перемоги і не впасти у відчай від поразки</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Друзів</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Власну мову</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Яку рису Кіплінг вважає найважчою для збереження, коли всі навколо сумніваються у тобі?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Силу</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Власну впевненість і спокій — «коли всі навколо утрачають голову, а ти зберігаєш розум»</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Гроші</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Красу</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що Кіплінг говорить про поразки і невдачі у вірші «Якщо…»?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Поразки слід уникати будь-якою ціною</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Справжня людина вміє почати спочатку після поразки, не скаржачись</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поразки — це ганьба</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поразок слід соромитись</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як Кіплінг описує ставлення до брехні й обману від інших людей?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Мстись за брехню</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Збережи гідність, навіть якщо тебе зрадили брехуни — не поступайся собі у відповідь</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Не звертай уваги</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Виправдай брехунів</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Яке відоме британське місце вшановує цитату з «Якщо…» Кіплінга?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Парламент</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тенісний корт Вімблдону, де над входом до гравців написані слова про тріумф і катастрофу</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вестмінстерське абатство</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Букінгемський палац</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому «Якщо…» залишається актуальним понад сто років після написання?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо про нього вийшло багато фільмів</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо випробування, які описує вірш — зрада, поразка, успіх, сумнів — є постійними у житті кожної людини</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо він короткий</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо він легко запам'ятовується</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що спільного у моральному посланні «Балади» і «Якщо…»?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого спільного</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва стверджують, що внутрішня гідність і характер важливіші за зовнішні ознаки — походження, культуру, успіх</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Обидва про поразку</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Обидва про гроші</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що таке «дидактична поезія» і чому «Якщо…» є її зразком?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Поезія для дітей</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Поезія, що навчає моральних істин через художні образи, а не сухі правила</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поезія без сенсу</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поезія лише про природу</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Яку педагогічну цінність має «Якщо…» для учнів 7 класу?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Жодної особливої</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вірш пропонує конкретний моральний орієнтир для підлітків, що вчаться долати перші серйозні випробування</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вчить граматики</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Готує до іспитів</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чи суперечить суперечливість образу Кіплінга у сучасних дискусіях цінності його кращих текстів?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Так, треба заборонити Кіплінга</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ні — важливо вміти читати текст критично, розуміючи його контекст і водночас бачити непроминальну людську цінність у «Якщо…»</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Так, бо всі його твори погані</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ні, бо Кіплінг ніколи не помилявся</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яке місце займає Кіплінг у дитячій і підлітковій літературі?</t>
+          <t>Кіплінг займає особливе місце у дитячій та підлітковій літературі як автор «Книги джунглів», «Кіма» та численних оповідань.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яка суперечність у образі Кіплінга існує в сучасній дискусії?</t>
+          <t>Суперечність у образі Кіплінга полягає у тому, що поруч із гуманістичними текстами у нього є твори, що відображають колоніальний погляд.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку педагогічну цінність має «Якщо…» для підлітків?</t>
+          <t>«Якщо…» Кіплінга не має жодної педагогічної цінності для підлітків і вивчається лише заради знайомства з автором.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Якщо…»?</t>
+          <t>Головна ідея «Якщо…» — внутрішня рівновага, гідність і вміння зберігати себе в будь-яких обставинах роблять людину по-справжньому зрілою.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Чому «Якщо…» Кіплінга залишається актуальним понад сто років?</t>
+          <t>«Якщо…» залишається актуальним, бо описані випробування — зрада, поразка, сумнів — є постійними в людському житті.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між «Баладою про Схід і Захід» і «Якщо…»?</t>
+          <t>І «Балада», і «Якщо…» стверджують, що зовнішнє походження і культура важливіші за внутрішній характер людини.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які чесноти оспівує вірш «Якщо…»?</t>
+          <t>Що стверджують твори Кіплінга у програмі?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Стійкість перед невдачею</t>
+          <t>Шляхетні люди знаходять спільну мову поза межами культурних відмінностей</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Самоконтроль і рівновага</t>
+          <t>Справжня людина зберігає рівновагу в тріумфі і поразці</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Фізична сила</t>
+          <t>Кіплінг закликає до колоніальної зверхності</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Чесність і скромність</t>
+          <t>Гідність і характер важливіші за походження і успіх</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Поразку успіх зраду друзів брехню — і вміння зберігати рівновагу і гідність у всіх крайнощах</t>
+          <t>Поразку успіх зраду друзів брехню</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>«Зустрічати тріумф і катастрофу і ставитись до цих двох обманщиків однаково» — перемога і поразка рівні</t>
+          <t>«Зустрічати тріумф і катастрофу і ставитись до цих двох обманщиків однаково»</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Поезія що навчає передає моральні ідеї через художні образи — «Якщо…» один з найвідоміших зразків</t>
+          <t>Поезія що навчає передає моральні ідеї через художні образи</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
